--- a/data/data_2024-01-22_LSR3_H.xlsx
+++ b/data/data_2024-01-22_LSR3_H.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:EC26"/>
+  <dimension ref="A1:EH26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,655 +367,680 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>study_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>study_doi</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>main</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>study_design</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>drug_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dose</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sample_n</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>randomized_n</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>age_mean</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>female_n</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>duration_weeks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>duration_unit</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>response_e</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>response_n</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>relapse_e</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>relapse_n</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dropout_any_e</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dropout_any_n</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dropout_ae_e</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dropout_ae_n</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>death_e</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>death_n</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>serious_e</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>serious_n</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>overall_scale_name</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>overall_n</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>overall_baseline</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>overall_baseline_n</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>overall_mean</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>overall_sd</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>overall_change_endpoint</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>overall_completer</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>overall_sd_origin</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>positive_scale_name</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>positive_n</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>positive_baseline</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>positive_mean</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>positive_sd</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>positive_change_endpoint</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>positive_completer</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>positive_sd_origin</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>negative_scale_name</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>negative_n</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>negative_baseline</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>negative_mean</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>negative_sd</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>negative_change_endpoint</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>negative_completer</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>negative_sd_origin</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>functioning_scale_name</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>functioning_n</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>functioning_baseline</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>functioning_mean</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>functioning_sd</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>functioning_change_endpoint</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>functioning_completer</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>functioning_sd_origin</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>cognition_scale_name</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>cognition_n</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>cognition_baseline</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>cognition_mean</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>cognition_sd</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>cognition_change_endpoint</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>cognition_completer</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>cognition_sd_origin</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>depression_scale_name</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>depression_n</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>depression_baseline_n</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>depression_baseline</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>depression_mean</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>depression_sd</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>depression_change_endpoint</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>depression_completer</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>depression_sd_origin</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>weight_scale_name</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>weight_n</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>weight_baseline</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>weight_mean</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>weight_sd</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>weight_change_endpoint</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>weight_completer</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>weight_sd_origin</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Timepoint</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>prolactin_scale_name</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>prolactin_n</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>prolactin_baseline</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>prolactin_mean</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>prolactin_sd</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>prolactin_change_endpoint</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>prolactin_completer</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>prolactin_sd_origin</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>adverse_event_e</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>adverse_event_n</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>anticholinergic_symptom_e</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>anticholinergic_symptom_n</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>anxiety_e</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>anxiety_n</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>dizziness_e</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>dizziness_n</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>headache_e</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>headache_n</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>nausea_vomitting_e</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>nausea_vomitting_n</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>sedation_e</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>sedation_n</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>hyperprolactinemia_e</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>hyperprolactinemia_n</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>qtc_prolongation_e</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>qtc_prolongation_n</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>agitation_e</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>agitation_n</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>hypotension_e</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>hypotension_n</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>insomnia_e</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>insomnia_n</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>akathisia_e</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>akathisia_n</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>eps_symptoms_e</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>eps_symptoms_n</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>weight_increased_e</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>weight_increased_n</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>drug_new</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>timepoint</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>comparison_data</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>qtc_md_point</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>qtc_md_se</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>study_name_drug</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>crossover_periods</t>
         </is>
@@ -1033,279 +1058,292 @@
         </is>
       </c>
       <c r="C2">
+        <v>2023</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10.1212/CPJ.0000000000200175</t>
+        </is>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>47.5</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Parkinson Disease Psychosis</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>25</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>70.7</t>
         </is>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>4</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>6</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>NPI total</t>
         </is>
       </c>
-      <c r="AG2">
+      <c r="AJ2">
         <v>23</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>-11.5</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>20.12</v>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
         <is>
           <t>SAPS-PD</t>
         </is>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>24</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>13.1</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>-2.5</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>7.94</v>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
         <is>
           <t>MMSE</t>
         </is>
       </c>
-      <c r="BM2">
+      <c r="BQ2">
         <v>23</v>
       </c>
-      <c r="BN2">
+      <c r="BR2">
         <v>-25.1</v>
       </c>
-      <c r="BO2">
+      <c r="BS2">
         <v>0.8</v>
       </c>
-      <c r="BP2">
+      <c r="BT2">
         <v>2.2</v>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CS2">
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CX2">
         <v>18</v>
       </c>
-      <c r="CT2">
+      <c r="CY2">
         <v>25</v>
       </c>
-      <c r="CY2">
+      <c r="DD2">
         <v>4</v>
       </c>
-      <c r="CZ2">
+      <c r="DE2">
         <v>25</v>
       </c>
-      <c r="DC2">
+      <c r="DH2">
         <v>3</v>
       </c>
-      <c r="DD2">
+      <c r="DI2">
         <v>25</v>
       </c>
-      <c r="DE2">
+      <c r="DJ2">
         <v>2</v>
       </c>
-      <c r="DF2">
+      <c r="DK2">
         <v>25</v>
       </c>
-      <c r="DM2">
+      <c r="DR2">
         <v>13</v>
       </c>
-      <c r="DN2">
+      <c r="DS2">
         <v>25</v>
       </c>
-      <c r="DO2">
+      <c r="DT2">
         <v>2</v>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
         <is>
           <t>Isaacson (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EC2">
+      <c r="EH2">
         <v>1</v>
       </c>
     </row>
@@ -1321,294 +1359,307 @@
         </is>
       </c>
       <c r="C3">
+        <v>2023</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10.1212/CPJ.0000000000200175</t>
+        </is>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Parkinson Disease Psychosis</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>70.7</t>
         </is>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>1</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>6</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>NPI total</t>
         </is>
       </c>
-      <c r="AG3">
+      <c r="AJ3">
         <v>14</v>
       </c>
-      <c r="AI3">
+      <c r="AM3">
         <v>-17.3</v>
       </c>
-      <c r="AJ3">
+      <c r="AN3">
         <v>19.57</v>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
         <is>
           <t>SAPS-PD</t>
         </is>
       </c>
-      <c r="AO3">
+      <c r="AS3">
         <v>14</v>
       </c>
-      <c r="AP3">
+      <c r="AT3">
         <v>14.7</v>
       </c>
-      <c r="AQ3">
+      <c r="AU3">
         <v>-1.4</v>
       </c>
-      <c r="AR3">
+      <c r="AV3">
         <v>7.71</v>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>MMSE</t>
         </is>
       </c>
-      <c r="BM3">
+      <c r="BQ3">
         <v>14</v>
       </c>
-      <c r="BN3">
+      <c r="BR3">
         <v>-24.7</v>
       </c>
-      <c r="BO3">
+      <c r="BS3">
         <v>-0.3</v>
       </c>
-      <c r="BP3">
+      <c r="BT3">
         <v>1.99</v>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CS3">
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CX3">
         <v>12</v>
       </c>
-      <c r="CT3">
+      <c r="CY3">
         <v>14</v>
       </c>
-      <c r="CW3">
+      <c r="DB3">
         <v>0</v>
       </c>
-      <c r="CX3">
+      <c r="DC3">
         <v>14</v>
       </c>
-      <c r="CY3">
+      <c r="DD3">
         <v>1</v>
       </c>
-      <c r="CZ3">
+      <c r="DE3">
         <v>14</v>
       </c>
-      <c r="DC3">
+      <c r="DH3">
         <v>1</v>
       </c>
-      <c r="DD3">
+      <c r="DI3">
         <v>14</v>
       </c>
-      <c r="DE3">
+      <c r="DJ3">
         <v>2</v>
       </c>
-      <c r="DF3">
+      <c r="DK3">
         <v>14</v>
       </c>
-      <c r="DK3">
+      <c r="DP3">
         <v>1</v>
       </c>
-      <c r="DL3">
+      <c r="DQ3">
         <v>14</v>
       </c>
-      <c r="DM3">
+      <c r="DR3">
         <v>11</v>
       </c>
-      <c r="DN3">
+      <c r="DS3">
         <v>14</v>
       </c>
-      <c r="DO3">
+      <c r="DT3">
         <v>1</v>
       </c>
-      <c r="DP3">
+      <c r="DU3">
         <v>14</v>
       </c>
-      <c r="DW3" t="inlineStr">
+      <c r="EB3" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="DX3" t="inlineStr">
+      <c r="EC3" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB3" t="inlineStr">
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
         <is>
           <t>Isaacson (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EC3">
+      <c r="EH3">
         <v>1</v>
       </c>
     </row>
@@ -1624,413 +1675,432 @@
         </is>
       </c>
       <c r="C4">
+        <v>2020</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1056/nejmoa1911772</t>
+        </is>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>50-75</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>245</t>
         </is>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>120</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>30.3</t>
         </is>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>43</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>4</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG4">
+      <c r="AJ4">
         <v>120</v>
       </c>
-      <c r="AH4">
+      <c r="AK4">
         <v>101.4</v>
       </c>
-      <c r="AI4">
+      <c r="AL4">
+        <v>120</v>
+      </c>
+      <c r="AM4">
         <v>-17.2</v>
       </c>
-      <c r="AJ4">
+      <c r="AN4">
         <v>18.63</v>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
         <is>
           <t>PANSS positive</t>
         </is>
       </c>
-      <c r="AO4">
+      <c r="AS4">
         <v>120</v>
       </c>
-      <c r="AP4">
+      <c r="AT4">
         <v>25.8</v>
       </c>
-      <c r="AQ4">
+      <c r="AU4">
         <v>-5.5</v>
       </c>
-      <c r="AR4">
+      <c r="AV4">
         <v>5.48</v>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="AW4">
+      <c r="BA4">
         <v>120</v>
       </c>
-      <c r="AX4">
+      <c r="BB4">
         <v>24.7</v>
       </c>
-      <c r="AY4">
+      <c r="BC4">
         <v>-3.1</v>
       </c>
-      <c r="AZ4">
+      <c r="BD4">
         <v>4.38</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
         <is>
           <t>MADRS</t>
         </is>
       </c>
-      <c r="BU4">
+      <c r="BY4">
         <v>120</v>
       </c>
-      <c r="BV4">
+      <c r="BZ4">
+        <v>120</v>
+      </c>
+      <c r="CA4">
         <v>13.1</v>
       </c>
-      <c r="BW4">
+      <c r="CB4">
         <v>-3.3</v>
       </c>
-      <c r="BX4">
+      <c r="CC4">
         <v>6.57</v>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
         <is>
           <t>weight kg</t>
         </is>
       </c>
-      <c r="CC4">
+      <c r="CH4">
         <v>120</v>
       </c>
-      <c r="CD4">
+      <c r="CI4">
         <v>75.40000000000001</v>
       </c>
-      <c r="CE4">
+      <c r="CJ4">
         <v>0.3</v>
       </c>
-      <c r="CF4">
+      <c r="CK4">
         <v>1.9</v>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
         <is>
           <t>4 weeks</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>prolactin levels ng/ml</t>
         </is>
       </c>
-      <c r="CL4">
+      <c r="CQ4">
         <v>114</v>
       </c>
-      <c r="CN4">
+      <c r="CS4">
         <v>-1.965789473684211</v>
       </c>
-      <c r="CO4">
+      <c r="CT4">
         <v>28</v>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CS4">
+      <c r="CX4">
         <v>55</v>
       </c>
-      <c r="CT4">
+      <c r="CY4">
         <v>120</v>
       </c>
-      <c r="CW4">
+      <c r="DB4">
         <v>2</v>
       </c>
-      <c r="CX4">
+      <c r="DC4">
         <v>120</v>
       </c>
-      <c r="DA4">
+      <c r="DF4">
         <v>11</v>
       </c>
-      <c r="DB4">
+      <c r="DG4">
         <v>120</v>
       </c>
-      <c r="DC4">
+      <c r="DH4">
         <v>6</v>
       </c>
-      <c r="DD4">
+      <c r="DI4">
         <v>120</v>
       </c>
-      <c r="DE4">
+      <c r="DJ4">
         <v>8</v>
       </c>
-      <c r="DF4">
+      <c r="DK4">
         <v>120</v>
       </c>
-      <c r="DI4">
+      <c r="DN4">
         <v>0</v>
       </c>
-      <c r="DJ4">
+      <c r="DO4">
         <v>120</v>
       </c>
-      <c r="DK4">
+      <c r="DP4">
         <v>6</v>
       </c>
-      <c r="DL4">
+      <c r="DQ4">
         <v>120</v>
       </c>
-      <c r="DO4">
+      <c r="DT4">
         <v>4</v>
       </c>
-      <c r="DP4">
+      <c r="DU4">
         <v>120</v>
       </c>
-      <c r="DQ4">
+      <c r="DV4">
         <v>1</v>
       </c>
-      <c r="DR4">
+      <c r="DW4">
         <v>120</v>
       </c>
-      <c r="DS4">
+      <c r="DX4">
         <v>4</v>
       </c>
-      <c r="DT4">
+      <c r="DY4">
         <v>120</v>
       </c>
-      <c r="DU4">
+      <c r="DZ4">
         <v>1</v>
       </c>
-      <c r="DV4">
+      <c r="EA4">
         <v>120</v>
       </c>
-      <c r="DW4" t="inlineStr">
+      <c r="EB4" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX4" t="inlineStr">
+      <c r="EC4" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB4" t="inlineStr">
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
         <is>
           <t>Koblan (2020) - ulotaront</t>
         </is>
       </c>
-      <c r="EC4">
+      <c r="EH4">
         <v>1</v>
       </c>
     </row>
@@ -2046,413 +2116,432 @@
         </is>
       </c>
       <c r="C5">
+        <v>2020</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1056/nejmoa1911772</t>
+        </is>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>245</t>
         </is>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>125</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>30.3</t>
         </is>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>46</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>4</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG5">
+      <c r="AJ5">
         <v>125</v>
       </c>
-      <c r="AH5">
+      <c r="AK5">
         <v>99.7</v>
       </c>
-      <c r="AI5">
+      <c r="AL5">
+        <v>125</v>
+      </c>
+      <c r="AM5">
         <v>-9.699999999999999</v>
       </c>
-      <c r="AJ5">
+      <c r="AN5">
         <v>17.89</v>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
         <is>
           <t>PANSS positive</t>
         </is>
       </c>
-      <c r="AO5">
+      <c r="AS5">
         <v>125</v>
       </c>
-      <c r="AP5">
+      <c r="AT5">
         <v>25.4</v>
       </c>
-      <c r="AQ5">
+      <c r="AU5">
         <v>-3.9</v>
       </c>
-      <c r="AR5">
+      <c r="AV5">
         <v>5.59</v>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="AW5">
+      <c r="BA5">
         <v>125</v>
       </c>
-      <c r="AX5">
+      <c r="BB5">
         <v>24.9</v>
       </c>
-      <c r="AY5">
+      <c r="BC5">
         <v>-1.6</v>
       </c>
-      <c r="AZ5">
+      <c r="BD5">
         <v>4.47</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
         <is>
           <t>MADRS</t>
         </is>
       </c>
-      <c r="BU5">
+      <c r="BY5">
         <v>125</v>
       </c>
-      <c r="BV5">
+      <c r="BZ5">
+        <v>125</v>
+      </c>
+      <c r="CA5">
         <v>12.6</v>
       </c>
-      <c r="BW5">
+      <c r="CB5">
         <v>-1.6</v>
       </c>
-      <c r="BX5">
+      <c r="CC5">
         <v>6.71</v>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
         <is>
           <t>weight kg</t>
         </is>
       </c>
-      <c r="CC5">
+      <c r="CH5">
         <v>125</v>
       </c>
-      <c r="CD5">
+      <c r="CI5">
         <v>75.40000000000001</v>
       </c>
-      <c r="CE5">
+      <c r="CJ5">
         <v>-0.1</v>
       </c>
-      <c r="CF5">
+      <c r="CK5">
         <v>2.3</v>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
         <is>
           <t>4 weeks</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>prolactin levels ng/ml</t>
         </is>
       </c>
-      <c r="CL5">
+      <c r="CQ5">
         <v>113</v>
       </c>
-      <c r="CN5">
+      <c r="CS5">
         <v>-1.383805309734513</v>
       </c>
-      <c r="CO5">
+      <c r="CT5">
         <v>28</v>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CS5">
+      <c r="CX5">
         <v>63</v>
       </c>
-      <c r="CT5">
+      <c r="CY5">
         <v>125</v>
       </c>
-      <c r="CW5">
+      <c r="DB5">
         <v>9</v>
       </c>
-      <c r="CX5">
+      <c r="DC5">
         <v>125</v>
       </c>
-      <c r="DA5">
+      <c r="DF5">
         <v>15</v>
       </c>
-      <c r="DB5">
+      <c r="DG5">
         <v>125</v>
       </c>
-      <c r="DC5">
+      <c r="DH5">
         <v>4</v>
       </c>
-      <c r="DD5">
+      <c r="DI5">
         <v>125</v>
       </c>
-      <c r="DE5">
+      <c r="DJ5">
         <v>6</v>
       </c>
-      <c r="DF5">
+      <c r="DK5">
         <v>125</v>
       </c>
-      <c r="DI5">
+      <c r="DN5">
         <v>0</v>
       </c>
-      <c r="DJ5">
+      <c r="DO5">
         <v>125</v>
       </c>
-      <c r="DK5">
+      <c r="DP5">
         <v>6</v>
       </c>
-      <c r="DL5">
+      <c r="DQ5">
         <v>125</v>
       </c>
-      <c r="DO5">
+      <c r="DT5">
         <v>13</v>
       </c>
-      <c r="DP5">
+      <c r="DU5">
         <v>125</v>
       </c>
-      <c r="DQ5">
+      <c r="DV5">
         <v>0</v>
       </c>
-      <c r="DR5">
+      <c r="DW5">
         <v>125</v>
       </c>
-      <c r="DS5">
+      <c r="DX5">
         <v>4</v>
       </c>
-      <c r="DT5">
+      <c r="DY5">
         <v>125</v>
       </c>
-      <c r="DU5">
+      <c r="DZ5">
         <v>1</v>
       </c>
-      <c r="DV5">
+      <c r="EA5">
         <v>125</v>
       </c>
-      <c r="DW5" t="inlineStr">
+      <c r="EB5" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="DX5" t="inlineStr">
+      <c r="EC5" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB5" t="inlineStr">
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
         <is>
           <t>Koblan (2020) - ulotaront</t>
         </is>
       </c>
-      <c r="EC5">
+      <c r="EH5">
         <v>1</v>
       </c>
     </row>
@@ -2468,152 +2557,163 @@
         </is>
       </c>
       <c r="C6">
+        <v>2023</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>435</t>
         </is>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>144</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>&gt;18</t>
         </is>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>6</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>144</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>144</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG6">
+      <c r="AJ6">
         <v>142</v>
       </c>
-      <c r="AH6">
+      <c r="AK6">
         <v>102</v>
       </c>
-      <c r="AI6">
+      <c r="AL6">
+        <v>142</v>
+      </c>
+      <c r="AM6">
         <v>-16.9</v>
       </c>
-      <c r="AJ6">
+      <c r="AN6">
         <v>19.07</v>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="DW6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX6" t="inlineStr">
+      <c r="EC6" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB6" t="inlineStr">
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EC6">
+      <c r="EH6">
         <v>1</v>
       </c>
     </row>
@@ -2629,152 +2729,163 @@
         </is>
       </c>
       <c r="C7">
+        <v>2023</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>435</t>
         </is>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>145</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>&gt;18</t>
         </is>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>6</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG7">
+      <c r="AJ7">
         <v>145</v>
       </c>
-      <c r="AH7">
+      <c r="AK7">
         <v>102</v>
       </c>
-      <c r="AI7">
+      <c r="AL7">
+        <v>145</v>
+      </c>
+      <c r="AM7">
         <v>-19.6</v>
       </c>
-      <c r="AJ7">
+      <c r="AN7">
         <v>19.27</v>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="DW7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX7" t="inlineStr">
+      <c r="EC7" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB7" t="inlineStr">
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EC7">
+      <c r="EH7">
         <v>1</v>
       </c>
     </row>
@@ -2790,152 +2901,163 @@
         </is>
       </c>
       <c r="C8">
+        <v>2023</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>435</t>
         </is>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>146</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>&gt;18</t>
         </is>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>6</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG8">
+      <c r="AJ8">
         <v>145</v>
       </c>
-      <c r="AH8">
+      <c r="AK8">
         <v>102</v>
       </c>
-      <c r="AI8">
+      <c r="AL8">
+        <v>145</v>
+      </c>
+      <c r="AM8">
         <v>-19.3</v>
       </c>
-      <c r="AJ8">
+      <c r="AN8">
         <v>18.06</v>
       </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="DW8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="DX8" t="inlineStr">
+      <c r="EC8" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB8" t="inlineStr">
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EC8">
+      <c r="EH8">
         <v>1</v>
       </c>
     </row>
@@ -2951,152 +3073,163 @@
         </is>
       </c>
       <c r="C9">
+        <v>2023</v>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>464</t>
         </is>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>155</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>&gt;18</t>
         </is>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>6</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG9">
+      <c r="AJ9">
         <v>153</v>
       </c>
-      <c r="AH9">
+      <c r="AK9">
         <v>101</v>
       </c>
-      <c r="AI9">
+      <c r="AL9">
+        <v>153</v>
+      </c>
+      <c r="AM9">
         <v>-16.4</v>
       </c>
-      <c r="AJ9">
+      <c r="AN9">
         <v>18.55</v>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="DW9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX9" t="inlineStr">
+      <c r="EC9" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB9" t="inlineStr">
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EC9">
+      <c r="EH9">
         <v>1</v>
       </c>
     </row>
@@ -3112,152 +3245,163 @@
         </is>
       </c>
       <c r="C10">
+        <v>2023</v>
+      </c>
+      <c r="E10">
         <v>1</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>464</t>
         </is>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>154</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>&gt;18</t>
         </is>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>6</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG10">
+      <c r="AJ10">
         <v>152</v>
       </c>
-      <c r="AH10">
+      <c r="AK10">
         <v>100</v>
       </c>
-      <c r="AI10">
+      <c r="AL10">
+        <v>152</v>
+      </c>
+      <c r="AM10">
         <v>-18.1</v>
       </c>
-      <c r="AJ10">
+      <c r="AN10">
         <v>18.49</v>
       </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="DW10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX10" t="inlineStr">
+      <c r="EC10" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB10" t="inlineStr">
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EC10">
+      <c r="EH10">
         <v>1</v>
       </c>
     </row>
@@ -3273,152 +3417,163 @@
         </is>
       </c>
       <c r="C11">
+        <v>2023</v>
+      </c>
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>464</t>
         </is>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>155</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>&gt;18</t>
         </is>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>6</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG11">
+      <c r="AJ11">
         <v>155</v>
       </c>
-      <c r="AH11">
+      <c r="AK11">
         <v>100</v>
       </c>
-      <c r="AI11">
+      <c r="AL11">
+        <v>155</v>
+      </c>
+      <c r="AM11">
         <v>-14.3</v>
       </c>
-      <c r="AJ11">
+      <c r="AN11">
         <v>18.67</v>
       </c>
-      <c r="AK11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="DW11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="DX11" t="inlineStr">
+      <c r="EC11" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB11" t="inlineStr">
+      <c r="ED11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG11" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EC11">
+      <c r="EH11">
         <v>1</v>
       </c>
     </row>
@@ -3434,323 +3589,337 @@
         </is>
       </c>
       <c r="C12">
+        <v>2023</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>73</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>33.1</t>
         </is>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>19</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>4</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG12">
+      <c r="AJ12">
         <v>54</v>
       </c>
-      <c r="AH12">
+      <c r="AK12">
         <v>99.38</v>
       </c>
-      <c r="AI12">
+      <c r="AL12">
+        <v>72</v>
+      </c>
+      <c r="AM12">
         <v>88.69</v>
       </c>
-      <c r="AJ12">
+      <c r="AN12">
         <v>20.18</v>
       </c>
-      <c r="AK12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
         <is>
           <t>PANSS positive</t>
         </is>
       </c>
-      <c r="AO12">
+      <c r="AS12">
         <v>54</v>
       </c>
-      <c r="AP12">
+      <c r="AT12">
         <v>26.86</v>
       </c>
-      <c r="AQ12">
+      <c r="AU12">
         <v>23.61</v>
       </c>
-      <c r="AR12">
+      <c r="AV12">
         <v>6.64</v>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="AW12">
+      <c r="BA12">
         <v>54</v>
       </c>
-      <c r="AX12">
+      <c r="BB12">
         <v>24.1</v>
       </c>
-      <c r="AY12">
+      <c r="BC12">
         <v>22.65</v>
       </c>
-      <c r="AZ12">
+      <c r="BD12">
         <v>5.81</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BU12">
+      <c r="BY12">
         <v>54</v>
       </c>
-      <c r="BV12">
+      <c r="BZ12">
+        <v>72</v>
+      </c>
+      <c r="CA12">
         <v>11.58</v>
       </c>
-      <c r="BW12">
+      <c r="CB12">
         <v>9.56</v>
       </c>
-      <c r="BX12">
+      <c r="CC12">
         <v>4.03</v>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CS12">
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CX12">
         <v>23</v>
       </c>
-      <c r="CT12">
+      <c r="CY12">
         <v>72</v>
       </c>
-      <c r="CW12">
+      <c r="DB12">
         <v>6</v>
       </c>
-      <c r="CX12">
+      <c r="DC12">
         <v>72</v>
       </c>
-      <c r="DA12">
+      <c r="DF12">
         <v>4</v>
       </c>
-      <c r="DB12">
+      <c r="DG12">
         <v>72</v>
       </c>
-      <c r="DC12">
+      <c r="DH12">
         <v>4</v>
       </c>
-      <c r="DD12">
+      <c r="DI12">
         <v>72</v>
       </c>
-      <c r="DK12">
+      <c r="DP12">
         <v>2</v>
       </c>
-      <c r="DL12">
+      <c r="DQ12">
         <v>72</v>
       </c>
-      <c r="DO12">
+      <c r="DT12">
         <v>1</v>
       </c>
-      <c r="DP12">
+      <c r="DU12">
         <v>72</v>
       </c>
-      <c r="DU12">
+      <c r="DZ12">
         <v>1</v>
       </c>
-      <c r="DV12">
+      <c r="EA12">
         <v>72</v>
       </c>
-      <c r="DW12" t="inlineStr">
+      <c r="EB12" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="DX12" t="inlineStr">
+      <c r="EC12" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB12" t="inlineStr">
+      <c r="ED12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG12" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EC12">
+      <c r="EH12">
         <v>1</v>
       </c>
     </row>
@@ -3766,323 +3935,337 @@
         </is>
       </c>
       <c r="C13">
+        <v>2023</v>
+      </c>
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>ralmitaront</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>71</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>33.1</t>
         </is>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>19</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>4</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG13">
+      <c r="AJ13">
         <v>49</v>
       </c>
-      <c r="AH13">
+      <c r="AK13">
         <v>98.54000000000001</v>
       </c>
-      <c r="AI13">
+      <c r="AL13">
+        <v>65</v>
+      </c>
+      <c r="AM13">
         <v>88.94</v>
       </c>
-      <c r="AJ13">
+      <c r="AN13">
         <v>17.03</v>
       </c>
-      <c r="AK13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
         <is>
           <t>PANSS positive</t>
         </is>
       </c>
-      <c r="AO13">
+      <c r="AS13">
         <v>49</v>
       </c>
-      <c r="AP13">
+      <c r="AT13">
         <v>26.2</v>
       </c>
-      <c r="AQ13">
+      <c r="AU13">
         <v>23.41</v>
       </c>
-      <c r="AR13">
+      <c r="AV13">
         <v>6.14</v>
       </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="AW13">
+      <c r="BA13">
         <v>49</v>
       </c>
-      <c r="AX13">
+      <c r="BB13">
         <v>23.65</v>
       </c>
-      <c r="AY13">
+      <c r="BC13">
         <v>21.82</v>
       </c>
-      <c r="AZ13">
+      <c r="BD13">
         <v>5.85</v>
       </c>
-      <c r="BA13" t="inlineStr">
+      <c r="BE13" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BU13">
+      <c r="BY13">
         <v>49</v>
       </c>
-      <c r="BV13">
+      <c r="BZ13">
+        <v>65</v>
+      </c>
+      <c r="CA13">
         <v>12.91</v>
       </c>
-      <c r="BW13">
+      <c r="CB13">
         <v>9.880000000000001</v>
       </c>
-      <c r="BX13">
+      <c r="CC13">
         <v>4.15</v>
       </c>
-      <c r="BY13" t="inlineStr">
+      <c r="CD13" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CS13">
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CX13">
         <v>14</v>
       </c>
-      <c r="CT13">
+      <c r="CY13">
         <v>65</v>
       </c>
-      <c r="CW13">
+      <c r="DB13">
         <v>3</v>
       </c>
-      <c r="CX13">
+      <c r="DC13">
         <v>65</v>
       </c>
-      <c r="DA13">
+      <c r="DF13">
         <v>4</v>
       </c>
-      <c r="DB13">
+      <c r="DG13">
         <v>65</v>
       </c>
-      <c r="DC13">
+      <c r="DH13">
         <v>0</v>
       </c>
-      <c r="DD13">
+      <c r="DI13">
         <v>65</v>
       </c>
-      <c r="DK13">
+      <c r="DP13">
         <v>0</v>
       </c>
-      <c r="DL13">
+      <c r="DQ13">
         <v>65</v>
       </c>
-      <c r="DO13">
+      <c r="DT13">
         <v>3</v>
       </c>
-      <c r="DP13">
+      <c r="DU13">
         <v>65</v>
       </c>
-      <c r="DU13">
+      <c r="DZ13">
         <v>2</v>
       </c>
-      <c r="DV13">
+      <c r="EA13">
         <v>65</v>
       </c>
-      <c r="DW13" t="inlineStr">
+      <c r="EB13" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX13" t="inlineStr">
+      <c r="EC13" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB13" t="inlineStr">
+      <c r="ED13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG13" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EC13">
+      <c r="EH13">
         <v>1</v>
       </c>
     </row>
@@ -4098,323 +4281,337 @@
         </is>
       </c>
       <c r="C14">
+        <v>2023</v>
+      </c>
+      <c r="E14">
         <v>1</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>ralmitaront</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>69</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>33.1</t>
         </is>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>15</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>4</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF14" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG14">
+      <c r="AJ14">
         <v>51</v>
       </c>
-      <c r="AH14">
+      <c r="AK14">
         <v>100.53</v>
       </c>
-      <c r="AI14">
+      <c r="AL14">
+        <v>68</v>
+      </c>
+      <c r="AM14">
         <v>85.18000000000001</v>
       </c>
-      <c r="AJ14">
+      <c r="AN14">
         <v>17.67</v>
       </c>
-      <c r="AK14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
         <is>
           <t>PANSS positive</t>
         </is>
       </c>
-      <c r="AO14">
+      <c r="AS14">
         <v>51</v>
       </c>
-      <c r="AP14">
+      <c r="AT14">
         <v>27.26</v>
       </c>
-      <c r="AQ14">
+      <c r="AU14">
         <v>22.22</v>
       </c>
-      <c r="AR14">
+      <c r="AV14">
         <v>6.5</v>
       </c>
-      <c r="AS14" t="inlineStr">
+      <c r="AW14" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="AW14">
+      <c r="BA14">
         <v>51</v>
       </c>
-      <c r="AX14">
+      <c r="BB14">
         <v>24.59</v>
       </c>
-      <c r="AY14">
+      <c r="BC14">
         <v>22.53</v>
       </c>
-      <c r="AZ14">
+      <c r="BD14">
         <v>5.41</v>
       </c>
-      <c r="BA14" t="inlineStr">
+      <c r="BE14" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BU14">
+      <c r="BY14">
         <v>51</v>
       </c>
-      <c r="BV14">
+      <c r="BZ14">
+        <v>68</v>
+      </c>
+      <c r="CA14">
         <v>11.54</v>
       </c>
-      <c r="BW14">
+      <c r="CB14">
         <v>9.06</v>
       </c>
-      <c r="BX14">
+      <c r="CC14">
         <v>4.08</v>
       </c>
-      <c r="BY14" t="inlineStr">
+      <c r="CD14" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BZ14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CS14">
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CX14">
         <v>23</v>
       </c>
-      <c r="CT14">
+      <c r="CY14">
         <v>68</v>
       </c>
-      <c r="CW14">
+      <c r="DB14">
         <v>2</v>
       </c>
-      <c r="CX14">
+      <c r="DC14">
         <v>68</v>
       </c>
-      <c r="DA14">
+      <c r="DF14">
         <v>5</v>
       </c>
-      <c r="DB14">
+      <c r="DG14">
         <v>68</v>
       </c>
-      <c r="DC14">
+      <c r="DH14">
         <v>2</v>
       </c>
-      <c r="DD14">
+      <c r="DI14">
         <v>68</v>
       </c>
-      <c r="DK14">
+      <c r="DP14">
         <v>8</v>
       </c>
-      <c r="DL14">
+      <c r="DQ14">
         <v>68</v>
       </c>
-      <c r="DO14">
+      <c r="DT14">
         <v>5</v>
       </c>
-      <c r="DP14">
+      <c r="DU14">
         <v>68</v>
       </c>
-      <c r="DU14">
+      <c r="DZ14">
         <v>0</v>
       </c>
-      <c r="DV14">
+      <c r="EA14">
         <v>68</v>
       </c>
-      <c r="DW14" t="inlineStr">
+      <c r="EB14" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX14" t="inlineStr">
+      <c r="EC14" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB14" t="inlineStr">
+      <c r="ED14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG14" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EC14">
+      <c r="EH14">
         <v>1</v>
       </c>
     </row>
@@ -4430,323 +4627,337 @@
         </is>
       </c>
       <c r="C15">
+        <v>2023</v>
+      </c>
+      <c r="E15">
         <v>1</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>risperidone</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>acute</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>74</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>33.1</t>
         </is>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>18</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>4</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
         <is>
           <t>Some concerns</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
           <t>PANSS total</t>
         </is>
       </c>
-      <c r="AG15">
+      <c r="AJ15">
         <v>56</v>
       </c>
-      <c r="AH15">
+      <c r="AK15">
         <v>100.03</v>
       </c>
-      <c r="AI15">
+      <c r="AL15">
+        <v>71</v>
+      </c>
+      <c r="AM15">
         <v>78.04000000000001</v>
       </c>
-      <c r="AJ15">
+      <c r="AN15">
         <v>15.78</v>
       </c>
-      <c r="AK15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
         <is>
           <t>PANSS positive</t>
         </is>
       </c>
-      <c r="AO15">
+      <c r="AS15">
         <v>56</v>
       </c>
-      <c r="AP15">
+      <c r="AT15">
         <v>27.49</v>
       </c>
-      <c r="AQ15">
+      <c r="AU15">
         <v>19.52</v>
       </c>
-      <c r="AR15">
+      <c r="AV15">
         <v>5.11</v>
       </c>
-      <c r="AS15" t="inlineStr">
+      <c r="AW15" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="AW15">
+      <c r="BA15">
         <v>56</v>
       </c>
-      <c r="AX15">
+      <c r="BB15">
         <v>23.65</v>
       </c>
-      <c r="AY15">
+      <c r="BC15">
         <v>21.45</v>
       </c>
-      <c r="AZ15">
+      <c r="BD15">
         <v>5.13</v>
       </c>
-      <c r="BA15" t="inlineStr">
+      <c r="BE15" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BU15">
+      <c r="BY15">
         <v>56</v>
       </c>
-      <c r="BV15">
+      <c r="BZ15">
+        <v>71</v>
+      </c>
+      <c r="CA15">
         <v>12.58</v>
       </c>
-      <c r="BW15">
+      <c r="CB15">
         <v>8.5</v>
       </c>
-      <c r="BX15">
+      <c r="CC15">
         <v>4.09</v>
       </c>
-      <c r="BY15" t="inlineStr">
+      <c r="CD15" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CS15">
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CX15">
         <v>36</v>
       </c>
-      <c r="CT15">
+      <c r="CY15">
         <v>71</v>
       </c>
-      <c r="CW15">
+      <c r="DB15">
         <v>5</v>
       </c>
-      <c r="CX15">
+      <c r="DC15">
         <v>71</v>
       </c>
-      <c r="DA15">
+      <c r="DF15">
         <v>6</v>
       </c>
-      <c r="DB15">
+      <c r="DG15">
         <v>71</v>
       </c>
-      <c r="DC15">
+      <c r="DH15">
         <v>6</v>
       </c>
-      <c r="DD15">
+      <c r="DI15">
         <v>71</v>
       </c>
-      <c r="DK15">
+      <c r="DP15">
         <v>0</v>
       </c>
-      <c r="DL15">
+      <c r="DQ15">
         <v>71</v>
       </c>
-      <c r="DO15">
+      <c r="DT15">
         <v>5</v>
       </c>
-      <c r="DP15">
+      <c r="DU15">
         <v>71</v>
       </c>
-      <c r="DU15">
+      <c r="DZ15">
         <v>8</v>
       </c>
-      <c r="DV15">
+      <c r="EA15">
         <v>71</v>
       </c>
-      <c r="DW15" t="inlineStr">
+      <c r="EB15" t="inlineStr">
         <is>
           <t>D2 antipsychotic</t>
         </is>
       </c>
-      <c r="DX15" t="inlineStr">
+      <c r="EC15" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="DY15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB15" t="inlineStr">
+      <c r="ED15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG15" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EC15">
+      <c r="EH15">
         <v>1</v>
       </c>
     </row>
@@ -4762,150 +4973,163 @@
         </is>
       </c>
       <c r="C16">
+        <v>2023</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41537-023-00385-6</t>
+        </is>
+      </c>
+      <c r="E16">
         <v>1</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Healthy volunteers</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>34</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>29.2</t>
         </is>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>18</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>0.14</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="CS16">
+      <c r="CX16">
         <v>16</v>
       </c>
-      <c r="CT16">
+      <c r="CY16">
         <v>34</v>
       </c>
-      <c r="CU16">
+      <c r="CZ16">
         <v>0</v>
       </c>
-      <c r="CV16">
+      <c r="DA16">
         <v>34</v>
       </c>
-      <c r="CW16">
+      <c r="DB16">
         <v>0</v>
       </c>
-      <c r="CX16">
+      <c r="DC16">
         <v>34</v>
       </c>
-      <c r="CY16">
+      <c r="DD16">
         <v>2</v>
       </c>
-      <c r="CZ16">
+      <c r="DE16">
         <v>34</v>
       </c>
-      <c r="DA16">
+      <c r="DF16">
         <v>7</v>
       </c>
-      <c r="DB16">
+      <c r="DG16">
         <v>34</v>
       </c>
-      <c r="DC16">
+      <c r="DH16">
         <v>0</v>
       </c>
-      <c r="DD16">
+      <c r="DI16">
         <v>34</v>
       </c>
-      <c r="DE16">
+      <c r="DJ16">
         <v>5</v>
       </c>
-      <c r="DF16">
+      <c r="DK16">
         <v>34</v>
       </c>
-      <c r="DW16" t="inlineStr">
+      <c r="EB16" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="DX16" t="inlineStr">
+      <c r="EC16" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="DY16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB16" t="inlineStr">
+      <c r="ED16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EC16">
+      <c r="EH16">
         <v>1</v>
       </c>
     </row>
@@ -4921,150 +5145,163 @@
         </is>
       </c>
       <c r="C17">
+        <v>2023</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41537-023-00385-6</t>
+        </is>
+      </c>
+      <c r="E17">
         <v>1</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Healthy volunteers</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>35</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>27.4</t>
         </is>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>14</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>0.14</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="CS17">
+      <c r="CX17">
         <v>34</v>
       </c>
-      <c r="CT17">
+      <c r="CY17">
         <v>35</v>
       </c>
-      <c r="CU17">
+      <c r="CZ17">
         <v>5</v>
       </c>
-      <c r="CV17">
+      <c r="DA17">
         <v>35</v>
       </c>
-      <c r="CW17">
+      <c r="DB17">
         <v>0</v>
       </c>
-      <c r="CX17">
+      <c r="DC17">
         <v>35</v>
       </c>
-      <c r="CY17">
+      <c r="DD17">
         <v>10</v>
       </c>
-      <c r="CZ17">
+      <c r="DE17">
         <v>35</v>
       </c>
-      <c r="DA17">
+      <c r="DF17">
         <v>4</v>
       </c>
-      <c r="DB17">
+      <c r="DG17">
         <v>35</v>
       </c>
-      <c r="DC17">
+      <c r="DH17">
         <v>12</v>
       </c>
-      <c r="DD17">
+      <c r="DI17">
         <v>35</v>
       </c>
-      <c r="DE17">
+      <c r="DJ17">
         <v>21</v>
       </c>
-      <c r="DF17">
+      <c r="DK17">
         <v>35</v>
       </c>
-      <c r="DW17" t="inlineStr">
+      <c r="EB17" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX17" t="inlineStr">
+      <c r="EC17" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="DY17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB17" t="inlineStr">
+      <c r="ED17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG17" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EC17">
+      <c r="EH17">
         <v>1</v>
       </c>
     </row>
@@ -5080,150 +5317,163 @@
         </is>
       </c>
       <c r="C18">
+        <v>2023</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41537-023-00385-6</t>
+        </is>
+      </c>
+      <c r="E18">
         <v>1</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>parallel-RCT</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>amisulpride</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Healthy volunteers</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>36</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>27.6</t>
         </is>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>13</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>0.14</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="CS18">
+      <c r="CX18">
         <v>15</v>
       </c>
-      <c r="CT18">
+      <c r="CY18">
         <v>36</v>
       </c>
-      <c r="CU18">
+      <c r="CZ18">
         <v>0</v>
       </c>
-      <c r="CV18">
+      <c r="DA18">
         <v>36</v>
       </c>
-      <c r="CW18">
+      <c r="DB18">
         <v>3</v>
       </c>
-      <c r="CX18">
+      <c r="DC18">
         <v>36</v>
       </c>
-      <c r="CY18">
+      <c r="DD18">
         <v>1</v>
       </c>
-      <c r="CZ18">
+      <c r="DE18">
         <v>36</v>
       </c>
-      <c r="DA18">
+      <c r="DF18">
         <v>1</v>
       </c>
-      <c r="DB18">
+      <c r="DG18">
         <v>36</v>
       </c>
-      <c r="DC18">
+      <c r="DH18">
         <v>0</v>
       </c>
-      <c r="DD18">
+      <c r="DI18">
         <v>36</v>
       </c>
-      <c r="DE18">
+      <c r="DJ18">
         <v>5</v>
       </c>
-      <c r="DF18">
+      <c r="DK18">
         <v>36</v>
       </c>
-      <c r="DW18" t="inlineStr">
+      <c r="EB18" t="inlineStr">
         <is>
           <t>D2 antipsychotic</t>
         </is>
       </c>
-      <c r="DX18" t="inlineStr">
+      <c r="EC18" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="DY18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB18" t="inlineStr">
+      <c r="ED18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG18" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EC18">
+      <c r="EH18">
         <v>1</v>
       </c>
     </row>
@@ -5239,139 +5489,152 @@
         </is>
       </c>
       <c r="C19">
+        <v>2023</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://dx.doi.org/10.1111/cts.13512</t>
+        </is>
+      </c>
+      <c r="E19">
         <v>1</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>crossover-RCT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>68</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>48.3</t>
         </is>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>15</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>0.14</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="CS19">
+      <c r="CX19">
         <v>2</v>
       </c>
-      <c r="CT19">
+      <c r="CY19">
         <v>63</v>
       </c>
-      <c r="CY19">
+      <c r="DD19">
         <v>1</v>
       </c>
-      <c r="CZ19">
+      <c r="DE19">
         <v>63</v>
       </c>
-      <c r="DC19">
+      <c r="DH19">
         <v>1</v>
       </c>
-      <c r="DD19">
+      <c r="DI19">
         <v>63</v>
       </c>
-      <c r="DE19">
+      <c r="DJ19">
         <v>0</v>
       </c>
-      <c r="DF19">
+      <c r="DK19">
         <v>63</v>
       </c>
-      <c r="DI19">
+      <c r="DN19">
         <v>1</v>
       </c>
-      <c r="DJ19">
+      <c r="DO19">
         <v>59</v>
       </c>
-      <c r="DW19" t="inlineStr">
+      <c r="EB19" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="DX19" t="inlineStr">
+      <c r="EC19" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="DY19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="DZ19">
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EE19">
         <v>1.248958333333333</v>
       </c>
-      <c r="EA19">
+      <c r="EF19">
         <v>2.100625000000001</v>
       </c>
-      <c r="EB19" t="inlineStr">
+      <c r="EG19" t="inlineStr">
         <is>
           <t>Tsukada (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EC19">
+      <c r="EH19">
         <v>2</v>
       </c>
     </row>
@@ -5387,149 +5650,162 @@
         </is>
       </c>
       <c r="C20">
+        <v>2023</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://dx.doi.org/10.1111/cts.13512</t>
+        </is>
+      </c>
+      <c r="E20">
         <v>1</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>crossover-RCT</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Schizophrenia spectrum</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>68</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>48.3</t>
         </is>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>15</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>0.14</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="CS20">
+      <c r="CX20">
         <v>32</v>
       </c>
-      <c r="CT20">
+      <c r="CY20">
         <v>63</v>
       </c>
-      <c r="CY20">
+      <c r="DD20">
         <v>7</v>
       </c>
-      <c r="CZ20">
+      <c r="DE20">
         <v>63</v>
       </c>
-      <c r="DC20">
+      <c r="DH20">
         <v>16</v>
       </c>
-      <c r="DD20">
+      <c r="DI20">
         <v>63</v>
       </c>
-      <c r="DE20">
+      <c r="DJ20">
         <v>16</v>
       </c>
-      <c r="DF20">
+      <c r="DK20">
         <v>63</v>
       </c>
-      <c r="DI20">
+      <c r="DN20">
         <v>5</v>
       </c>
-      <c r="DJ20">
+      <c r="DO20">
         <v>62</v>
       </c>
-      <c r="DW20" t="inlineStr">
+      <c r="EB20" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX20" t="inlineStr">
+      <c r="EC20" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="DY20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="DZ20">
+      <c r="ED20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EE20">
         <v>1.248958333333333</v>
       </c>
-      <c r="EA20">
+      <c r="EF20">
         <v>2.100625000000001</v>
       </c>
-      <c r="EB20" t="inlineStr">
+      <c r="EG20" t="inlineStr">
         <is>
           <t>Tsukada (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EC20">
+      <c r="EH20">
         <v>2</v>
       </c>
     </row>
@@ -5545,138 +5821,151 @@
         </is>
       </c>
       <c r="C21">
+        <v>2021</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41398-021-01331-9</t>
+        </is>
+      </c>
+      <c r="E21">
         <v>1</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>crossover-RCT</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Healthy volunteers</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>12</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>0</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>0.14</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="CS21">
+      <c r="CX21">
         <v>1</v>
       </c>
-      <c r="CT21">
+      <c r="CY21">
         <v>12</v>
       </c>
-      <c r="DC21">
+      <c r="DH21">
         <v>1</v>
       </c>
-      <c r="DD21">
+      <c r="DI21">
         <v>12</v>
       </c>
-      <c r="DE21">
+      <c r="DJ21">
         <v>0</v>
       </c>
-      <c r="DF21">
+      <c r="DK21">
         <v>12</v>
       </c>
-      <c r="DG21">
+      <c r="DL21">
         <v>0</v>
       </c>
-      <c r="DH21">
+      <c r="DM21">
         <v>12</v>
       </c>
-      <c r="DI21">
+      <c r="DN21">
         <v>0</v>
       </c>
-      <c r="DJ21">
+      <c r="DO21">
         <v>12</v>
       </c>
-      <c r="DW21" t="inlineStr">
+      <c r="EB21" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX21" t="inlineStr">
+      <c r="EC21" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="DY21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB21" t="inlineStr">
+      <c r="ED21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG21" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EC21">
+      <c r="EH21">
         <v>2</v>
       </c>
     </row>
@@ -5692,138 +5981,151 @@
         </is>
       </c>
       <c r="C22">
+        <v>2021</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41398-021-01331-9</t>
+        </is>
+      </c>
+      <c r="E22">
         <v>1</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>crossover-RCT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Healthy volunteers</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>12</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>0</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>0.14</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="CS22">
+      <c r="CX22">
         <v>1</v>
       </c>
-      <c r="CT22">
+      <c r="CY22">
         <v>12</v>
       </c>
-      <c r="DC22">
+      <c r="DH22">
         <v>0</v>
       </c>
-      <c r="DD22">
+      <c r="DI22">
         <v>12</v>
       </c>
-      <c r="DE22">
+      <c r="DJ22">
         <v>1</v>
       </c>
-      <c r="DF22">
+      <c r="DK22">
         <v>12</v>
       </c>
-      <c r="DG22">
+      <c r="DL22">
         <v>0</v>
       </c>
-      <c r="DH22">
+      <c r="DM22">
         <v>12</v>
       </c>
-      <c r="DI22">
+      <c r="DN22">
         <v>0</v>
       </c>
-      <c r="DJ22">
+      <c r="DO22">
         <v>12</v>
       </c>
-      <c r="DW22" t="inlineStr">
+      <c r="EB22" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX22" t="inlineStr">
+      <c r="EC22" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="DY22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB22" t="inlineStr">
+      <c r="ED22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG22" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EC22">
+      <c r="EH22">
         <v>2</v>
       </c>
     </row>
@@ -5839,138 +6141,151 @@
         </is>
       </c>
       <c r="C23">
+        <v>2021</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41398-021-01331-9</t>
+        </is>
+      </c>
+      <c r="E23">
         <v>1</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>crossover-RCT</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Healthy volunteers</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>24</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>0</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>0.14</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="CS23">
+      <c r="CX23">
         <v>1</v>
       </c>
-      <c r="CT23">
+      <c r="CY23">
         <v>24</v>
       </c>
-      <c r="DC23">
+      <c r="DH23">
         <v>0</v>
       </c>
-      <c r="DD23">
+      <c r="DI23">
         <v>24</v>
       </c>
-      <c r="DE23">
+      <c r="DJ23">
         <v>0</v>
       </c>
-      <c r="DF23">
+      <c r="DK23">
         <v>24</v>
       </c>
-      <c r="DG23">
+      <c r="DL23">
         <v>0</v>
       </c>
-      <c r="DH23">
+      <c r="DM23">
         <v>24</v>
       </c>
-      <c r="DI23">
+      <c r="DN23">
         <v>0</v>
       </c>
-      <c r="DJ23">
+      <c r="DO23">
         <v>24</v>
       </c>
-      <c r="DW23" t="inlineStr">
+      <c r="EB23" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="DX23" t="inlineStr">
+      <c r="EC23" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="DY23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB23" t="inlineStr">
+      <c r="ED23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG23" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EC23">
+      <c r="EH23">
         <v>2</v>
       </c>
     </row>
@@ -5986,94 +6301,107 @@
         </is>
       </c>
       <c r="C24">
+        <v>2023</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://dx.doi.org/10.1016/j.sleep.2023.04.019</t>
+        </is>
+      </c>
+      <c r="E24">
         <v>1</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>crossover-RCT</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Narcolepsy-cataplexy</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>16</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>12</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>2</v>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="CS24">
+      <c r="CX24">
         <v>6</v>
       </c>
-      <c r="CT24">
+      <c r="CY24">
         <v>15</v>
       </c>
-      <c r="DW24" t="inlineStr">
+      <c r="EB24" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX24" t="inlineStr">
+      <c r="EC24" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="DY24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB24" t="inlineStr">
+      <c r="ED24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG24" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EC24">
+      <c r="EH24">
         <v>3</v>
       </c>
     </row>
@@ -6089,94 +6417,107 @@
         </is>
       </c>
       <c r="C25">
+        <v>2023</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://dx.doi.org/10.1016/j.sleep.2023.04.019</t>
+        </is>
+      </c>
+      <c r="E25">
         <v>0</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>crossover-RCT</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>ulotaront</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Narcolepsy-cataplexy</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>16</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>12</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>2</v>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="CS25">
+      <c r="CX25">
         <v>1</v>
       </c>
-      <c r="CT25">
+      <c r="CY25">
         <v>13</v>
       </c>
-      <c r="DW25" t="inlineStr">
+      <c r="EB25" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="DX25" t="inlineStr">
+      <c r="EC25" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="DY25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB25" t="inlineStr">
+      <c r="ED25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG25" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EC25">
+      <c r="EH25">
         <v>3</v>
       </c>
     </row>
@@ -6192,94 +6533,107 @@
         </is>
       </c>
       <c r="C26">
+        <v>2023</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://dx.doi.org/10.1016/j.sleep.2023.04.019</t>
+        </is>
+      </c>
+      <c r="E26">
         <v>1</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>crossover-RCT</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Narcolepsy-cataplexy</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>16</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>12</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>2</v>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>weeks</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="CS26">
+      <c r="CX26">
         <v>2</v>
       </c>
-      <c r="CT26">
+      <c r="CY26">
         <v>14</v>
       </c>
-      <c r="DW26" t="inlineStr">
+      <c r="EB26" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="DX26" t="inlineStr">
+      <c r="EC26" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="DY26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EB26" t="inlineStr">
+      <c r="ED26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EG26" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EC26">
+      <c r="EH26">
         <v>3</v>
       </c>
     </row>

--- a/data/data_2024-01-22_LSR3_H.xlsx
+++ b/data/data_2024-01-22_LSR3_H.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:EH26"/>
+  <dimension ref="A1:EM26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -582,465 +582,490 @@
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
+          <t>positive_baseline_n</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>positive_baseline</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>positive_mean</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>positive_sd</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>positive_change_endpoint</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>positive_completer</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>positive_sd_origin</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>negative_scale_name</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>negative_baseline_n</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>negative_n</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>negative_baseline</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>negative_mean</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>negative_sd</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>negative_change_endpoint</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>negative_completer</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>negative_sd_origin</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>functioning_scale_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>functioning_n</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>functioning_baseline</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>functioning_mean</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>functioning_sd</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>functioning_change_endpoint</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>functioning_completer</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>functioning_sd_origin</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>cognition_scale_name</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>cognition_n</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>cognition_baseline_n</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>cognition_baseline</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>cognition_mean</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>cognition_sd</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>cognition_change_endpoint</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>cognition_completer</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>cognition_sd_origin</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>depression_scale_name</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>depression_n</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>depression_baseline_n</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>depression_baseline</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>depression_mean</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>depression_sd</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>depression_change_endpoint</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>depression_completer</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>depression_sd_origin</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>weight_scale_name</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>weight_n</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>weight_baseline_n</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>weight_baseline</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>weight_mean</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>weight_sd</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>weight_change_endpoint</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>weight_completer</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>weight_sd_origin</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>Timepoint</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>prolactin_scale_name</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>prolactin_n</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>prolactin_baseline_n</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>prolactin_baseline</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>prolactin_mean</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>prolactin_sd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>prolactin_change_endpoint</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>prolactin_completer</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>prolactin_sd_origin</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>adverse_event_e</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>adverse_event_n</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>anticholinergic_symptom_e</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>anticholinergic_symptom_n</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>anxiety_e</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>anxiety_n</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>dizziness_e</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>dizziness_n</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>headache_e</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>headache_n</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>nausea_vomitting_e</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>nausea_vomitting_n</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>sedation_e</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>sedation_n</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>hyperprolactinemia_e</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>hyperprolactinemia_n</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>qtc_prolongation_e</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>qtc_prolongation_n</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>agitation_e</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>agitation_n</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>hypotension_e</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>hypotension_n</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>insomnia_e</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>insomnia_n</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>akathisia_e</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>akathisia_n</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>eps_symptoms_e</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>eps_symptoms_n</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>weight_increased_e</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>weight_increased_n</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>drug_new</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>timepoint</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>comparison_data</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>qtc_md_point</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>qtc_md_se</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>study_name_drug</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>crossover_periods</t>
         </is>
@@ -1235,115 +1260,121 @@
         <v>24</v>
       </c>
       <c r="AT2">
+        <v>24</v>
+      </c>
+      <c r="AU2">
         <v>13.1</v>
       </c>
-      <c r="AU2">
+      <c r="AV2">
         <v>-2.5</v>
       </c>
-      <c r="AV2">
+      <c r="AW2">
         <v>7.94</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>MMSE</t>
         </is>
       </c>
-      <c r="BQ2">
+      <c r="BS2">
         <v>23</v>
       </c>
-      <c r="BR2">
+      <c r="BT2">
+        <v>24</v>
+      </c>
+      <c r="BU2">
         <v>-25.1</v>
       </c>
-      <c r="BS2">
+      <c r="BV2">
         <v>0.8</v>
       </c>
-      <c r="BT2">
+      <c r="BW2">
         <v>2.2</v>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX2">
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC2">
         <v>18</v>
       </c>
-      <c r="CY2">
+      <c r="DD2">
         <v>25</v>
       </c>
-      <c r="DD2">
+      <c r="DI2">
         <v>4</v>
       </c>
-      <c r="DE2">
+      <c r="DJ2">
         <v>25</v>
       </c>
-      <c r="DH2">
+      <c r="DM2">
         <v>3</v>
       </c>
-      <c r="DI2">
+      <c r="DN2">
         <v>25</v>
       </c>
-      <c r="DJ2">
+      <c r="DO2">
         <v>2</v>
       </c>
-      <c r="DK2">
+      <c r="DP2">
         <v>25</v>
       </c>
-      <c r="DR2">
+      <c r="DW2">
         <v>13</v>
       </c>
-      <c r="DS2">
+      <c r="DX2">
         <v>25</v>
       </c>
-      <c r="DT2">
+      <c r="DY2">
         <v>2</v>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
         <is>
           <t>Isaacson (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH2">
+      <c r="EM2">
         <v>1</v>
       </c>
     </row>
@@ -1536,130 +1567,136 @@
         <v>14</v>
       </c>
       <c r="AT3">
+        <v>14</v>
+      </c>
+      <c r="AU3">
         <v>14.7</v>
       </c>
-      <c r="AU3">
+      <c r="AV3">
         <v>-1.4</v>
       </c>
-      <c r="AV3">
+      <c r="AW3">
         <v>7.71</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>MMSE</t>
         </is>
       </c>
-      <c r="BQ3">
+      <c r="BS3">
         <v>14</v>
       </c>
-      <c r="BR3">
+      <c r="BT3">
+        <v>14</v>
+      </c>
+      <c r="BU3">
         <v>-24.7</v>
       </c>
-      <c r="BS3">
+      <c r="BV3">
         <v>-0.3</v>
       </c>
-      <c r="BT3">
+      <c r="BW3">
         <v>1.99</v>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX3">
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC3">
         <v>12</v>
       </c>
-      <c r="CY3">
+      <c r="DD3">
         <v>14</v>
       </c>
-      <c r="DB3">
+      <c r="DG3">
         <v>0</v>
       </c>
-      <c r="DC3">
+      <c r="DH3">
         <v>14</v>
       </c>
-      <c r="DD3">
+      <c r="DI3">
         <v>1</v>
       </c>
-      <c r="DE3">
+      <c r="DJ3">
         <v>14</v>
       </c>
-      <c r="DH3">
+      <c r="DM3">
         <v>1</v>
       </c>
-      <c r="DI3">
+      <c r="DN3">
         <v>14</v>
       </c>
-      <c r="DJ3">
+      <c r="DO3">
         <v>2</v>
       </c>
-      <c r="DK3">
+      <c r="DP3">
         <v>14</v>
       </c>
-      <c r="DP3">
+      <c r="DU3">
         <v>1</v>
       </c>
-      <c r="DQ3">
+      <c r="DV3">
         <v>14</v>
       </c>
-      <c r="DR3">
+      <c r="DW3">
         <v>11</v>
       </c>
-      <c r="DS3">
+      <c r="DX3">
         <v>14</v>
       </c>
-      <c r="DT3">
+      <c r="DY3">
         <v>1</v>
       </c>
-      <c r="DU3">
+      <c r="DZ3">
         <v>14</v>
       </c>
-      <c r="EB3" t="inlineStr">
+      <c r="EG3" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC3" t="inlineStr">
+      <c r="EH3" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr">
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
         <is>
           <t>Isaacson (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH3">
+      <c r="EM3">
         <v>1</v>
       </c>
     </row>
@@ -1858,249 +1895,258 @@
         <v>120</v>
       </c>
       <c r="AT4">
+        <v>120</v>
+      </c>
+      <c r="AU4">
         <v>25.8</v>
       </c>
-      <c r="AU4">
+      <c r="AV4">
         <v>-5.5</v>
       </c>
-      <c r="AV4">
+      <c r="AW4">
         <v>5.48</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="BA4">
+      <c r="BB4">
         <v>120</v>
       </c>
-      <c r="BB4">
+      <c r="BC4">
+        <v>120</v>
+      </c>
+      <c r="BD4">
         <v>24.7</v>
       </c>
-      <c r="BC4">
+      <c r="BE4">
         <v>-3.1</v>
       </c>
-      <c r="BD4">
+      <c r="BF4">
         <v>4.38</v>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
         <is>
           <t>MADRS</t>
         </is>
       </c>
-      <c r="BY4">
+      <c r="CB4">
         <v>120</v>
       </c>
-      <c r="BZ4">
+      <c r="CC4">
         <v>120</v>
       </c>
-      <c r="CA4">
+      <c r="CD4">
         <v>13.1</v>
       </c>
-      <c r="CB4">
+      <c r="CE4">
         <v>-3.3</v>
       </c>
-      <c r="CC4">
+      <c r="CF4">
         <v>6.57</v>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>weight kg</t>
         </is>
       </c>
-      <c r="CH4">
+      <c r="CK4">
         <v>120</v>
       </c>
-      <c r="CI4">
+      <c r="CL4">
+        <v>120</v>
+      </c>
+      <c r="CM4">
         <v>75.40000000000001</v>
       </c>
-      <c r="CJ4">
+      <c r="CN4">
         <v>0.3</v>
       </c>
-      <c r="CK4">
+      <c r="CO4">
         <v>1.9</v>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
         <is>
           <t>4 weeks</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>prolactin levels ng/ml</t>
         </is>
       </c>
-      <c r="CQ4">
+      <c r="CU4">
         <v>114</v>
       </c>
-      <c r="CS4">
+      <c r="CX4">
         <v>-1.965789473684211</v>
       </c>
-      <c r="CT4">
+      <c r="CY4">
         <v>28</v>
       </c>
-      <c r="CU4" t="inlineStr">
+      <c r="CZ4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CX4">
+      <c r="DC4">
         <v>55</v>
       </c>
-      <c r="CY4">
+      <c r="DD4">
         <v>120</v>
       </c>
-      <c r="DB4">
+      <c r="DG4">
         <v>2</v>
       </c>
-      <c r="DC4">
+      <c r="DH4">
         <v>120</v>
       </c>
-      <c r="DF4">
+      <c r="DK4">
         <v>11</v>
       </c>
-      <c r="DG4">
+      <c r="DL4">
         <v>120</v>
       </c>
-      <c r="DH4">
+      <c r="DM4">
         <v>6</v>
       </c>
-      <c r="DI4">
+      <c r="DN4">
         <v>120</v>
       </c>
-      <c r="DJ4">
+      <c r="DO4">
         <v>8</v>
       </c>
-      <c r="DK4">
+      <c r="DP4">
         <v>120</v>
       </c>
-      <c r="DN4">
+      <c r="DS4">
         <v>0</v>
       </c>
-      <c r="DO4">
+      <c r="DT4">
         <v>120</v>
       </c>
-      <c r="DP4">
+      <c r="DU4">
         <v>6</v>
       </c>
-      <c r="DQ4">
+      <c r="DV4">
         <v>120</v>
       </c>
-      <c r="DT4">
+      <c r="DY4">
         <v>4</v>
       </c>
-      <c r="DU4">
+      <c r="DZ4">
         <v>120</v>
       </c>
-      <c r="DV4">
+      <c r="EA4">
         <v>1</v>
       </c>
-      <c r="DW4">
+      <c r="EB4">
         <v>120</v>
       </c>
-      <c r="DX4">
+      <c r="EC4">
         <v>4</v>
       </c>
-      <c r="DY4">
+      <c r="ED4">
         <v>120</v>
       </c>
-      <c r="DZ4">
+      <c r="EE4">
         <v>1</v>
       </c>
-      <c r="EA4">
+      <c r="EF4">
         <v>120</v>
       </c>
-      <c r="EB4" t="inlineStr">
+      <c r="EG4" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC4" t="inlineStr">
+      <c r="EH4" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr">
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
         <is>
           <t>Koblan (2020) - ulotaront</t>
         </is>
       </c>
-      <c r="EH4">
+      <c r="EM4">
         <v>1</v>
       </c>
     </row>
@@ -2299,249 +2345,258 @@
         <v>125</v>
       </c>
       <c r="AT5">
+        <v>125</v>
+      </c>
+      <c r="AU5">
         <v>25.4</v>
       </c>
-      <c r="AU5">
+      <c r="AV5">
         <v>-3.9</v>
       </c>
-      <c r="AV5">
+      <c r="AW5">
         <v>5.59</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="BA5">
+      <c r="BB5">
         <v>125</v>
       </c>
-      <c r="BB5">
+      <c r="BC5">
+        <v>125</v>
+      </c>
+      <c r="BD5">
         <v>24.9</v>
       </c>
-      <c r="BC5">
+      <c r="BE5">
         <v>-1.6</v>
       </c>
-      <c r="BD5">
+      <c r="BF5">
         <v>4.47</v>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
         <is>
           <t>MADRS</t>
         </is>
       </c>
-      <c r="BY5">
+      <c r="CB5">
         <v>125</v>
       </c>
-      <c r="BZ5">
+      <c r="CC5">
         <v>125</v>
       </c>
-      <c r="CA5">
+      <c r="CD5">
         <v>12.6</v>
       </c>
-      <c r="CB5">
+      <c r="CE5">
         <v>-1.6</v>
       </c>
-      <c r="CC5">
+      <c r="CF5">
         <v>6.71</v>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>weight kg</t>
         </is>
       </c>
-      <c r="CH5">
+      <c r="CK5">
         <v>125</v>
       </c>
-      <c r="CI5">
+      <c r="CL5">
+        <v>125</v>
+      </c>
+      <c r="CM5">
         <v>75.40000000000001</v>
       </c>
-      <c r="CJ5">
+      <c r="CN5">
         <v>-0.1</v>
       </c>
-      <c r="CK5">
+      <c r="CO5">
         <v>2.3</v>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
         <is>
           <t>4 weeks</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>prolactin levels ng/ml</t>
         </is>
       </c>
-      <c r="CQ5">
+      <c r="CU5">
         <v>113</v>
       </c>
-      <c r="CS5">
+      <c r="CX5">
         <v>-1.383805309734513</v>
       </c>
-      <c r="CT5">
+      <c r="CY5">
         <v>28</v>
       </c>
-      <c r="CU5" t="inlineStr">
+      <c r="CZ5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CW5" t="inlineStr">
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CX5">
+      <c r="DC5">
         <v>63</v>
       </c>
-      <c r="CY5">
+      <c r="DD5">
         <v>125</v>
       </c>
-      <c r="DB5">
+      <c r="DG5">
         <v>9</v>
       </c>
-      <c r="DC5">
+      <c r="DH5">
         <v>125</v>
       </c>
-      <c r="DF5">
+      <c r="DK5">
         <v>15</v>
       </c>
-      <c r="DG5">
+      <c r="DL5">
         <v>125</v>
       </c>
-      <c r="DH5">
+      <c r="DM5">
         <v>4</v>
       </c>
-      <c r="DI5">
+      <c r="DN5">
         <v>125</v>
       </c>
-      <c r="DJ5">
+      <c r="DO5">
         <v>6</v>
       </c>
-      <c r="DK5">
+      <c r="DP5">
         <v>125</v>
       </c>
-      <c r="DN5">
+      <c r="DS5">
         <v>0</v>
       </c>
-      <c r="DO5">
+      <c r="DT5">
         <v>125</v>
       </c>
-      <c r="DP5">
+      <c r="DU5">
         <v>6</v>
       </c>
-      <c r="DQ5">
+      <c r="DV5">
         <v>125</v>
       </c>
-      <c r="DT5">
+      <c r="DY5">
         <v>13</v>
       </c>
-      <c r="DU5">
+      <c r="DZ5">
         <v>125</v>
       </c>
-      <c r="DV5">
+      <c r="EA5">
         <v>0</v>
       </c>
-      <c r="DW5">
+      <c r="EB5">
         <v>125</v>
       </c>
-      <c r="DX5">
+      <c r="EC5">
         <v>4</v>
       </c>
-      <c r="DY5">
+      <c r="ED5">
         <v>125</v>
       </c>
-      <c r="DZ5">
+      <c r="EE5">
         <v>1</v>
       </c>
-      <c r="EA5">
+      <c r="EF5">
         <v>125</v>
       </c>
-      <c r="EB5" t="inlineStr">
+      <c r="EG5" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC5" t="inlineStr">
+      <c r="EH5" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG5" t="inlineStr">
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
         <is>
           <t>Koblan (2020) - ulotaront</t>
         </is>
       </c>
-      <c r="EH5">
+      <c r="EM5">
         <v>1</v>
       </c>
     </row>
@@ -2693,27 +2748,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB6" t="inlineStr">
+      <c r="EG6" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC6" t="inlineStr">
+      <c r="EH6" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG6" t="inlineStr">
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH6">
+      <c r="EM6">
         <v>1</v>
       </c>
     </row>
@@ -2865,27 +2920,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB7" t="inlineStr">
+      <c r="EG7" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC7" t="inlineStr">
+      <c r="EH7" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG7" t="inlineStr">
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH7">
+      <c r="EM7">
         <v>1</v>
       </c>
     </row>
@@ -3037,27 +3092,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB8" t="inlineStr">
+      <c r="EG8" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC8" t="inlineStr">
+      <c r="EH8" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG8" t="inlineStr">
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH8">
+      <c r="EM8">
         <v>1</v>
       </c>
     </row>
@@ -3209,27 +3264,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB9" t="inlineStr">
+      <c r="EG9" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC9" t="inlineStr">
+      <c r="EH9" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG9" t="inlineStr">
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH9">
+      <c r="EM9">
         <v>1</v>
       </c>
     </row>
@@ -3381,27 +3436,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB10" t="inlineStr">
+      <c r="EG10" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC10" t="inlineStr">
+      <c r="EH10" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG10" t="inlineStr">
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH10">
+      <c r="EM10">
         <v>1</v>
       </c>
     </row>
@@ -3553,27 +3608,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB11" t="inlineStr">
+      <c r="EG11" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC11" t="inlineStr">
+      <c r="EH11" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG11" t="inlineStr">
+      <c r="EI11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL11" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH11">
+      <c r="EM11">
         <v>1</v>
       </c>
     </row>
@@ -3767,24 +3822,22 @@
         <v>54</v>
       </c>
       <c r="AT12">
+        <v>72</v>
+      </c>
+      <c r="AU12">
         <v>26.86</v>
       </c>
-      <c r="AU12">
+      <c r="AV12">
         <v>23.61</v>
       </c>
-      <c r="AV12">
+      <c r="AW12">
         <v>6.64</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3792,134 +3845,142 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="BA12">
+      <c r="BB12">
+        <v>72</v>
+      </c>
+      <c r="BC12">
         <v>54</v>
       </c>
-      <c r="BB12">
+      <c r="BD12">
         <v>24.1</v>
       </c>
-      <c r="BC12">
+      <c r="BE12">
         <v>22.65</v>
       </c>
-      <c r="BD12">
+      <c r="BF12">
         <v>5.81</v>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BY12">
+      <c r="CB12">
         <v>54</v>
       </c>
-      <c r="BZ12">
+      <c r="CC12">
         <v>72</v>
       </c>
-      <c r="CA12">
+      <c r="CD12">
         <v>11.58</v>
       </c>
-      <c r="CB12">
+      <c r="CE12">
         <v>9.56</v>
       </c>
-      <c r="CC12">
+      <c r="CF12">
         <v>4.03</v>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX12">
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC12">
         <v>23</v>
       </c>
-      <c r="CY12">
+      <c r="DD12">
         <v>72</v>
       </c>
-      <c r="DB12">
+      <c r="DG12">
         <v>6</v>
       </c>
-      <c r="DC12">
+      <c r="DH12">
         <v>72</v>
       </c>
-      <c r="DF12">
+      <c r="DK12">
         <v>4</v>
       </c>
-      <c r="DG12">
+      <c r="DL12">
         <v>72</v>
       </c>
-      <c r="DH12">
+      <c r="DM12">
         <v>4</v>
       </c>
-      <c r="DI12">
+      <c r="DN12">
         <v>72</v>
       </c>
-      <c r="DP12">
+      <c r="DU12">
         <v>2</v>
       </c>
-      <c r="DQ12">
+      <c r="DV12">
         <v>72</v>
       </c>
-      <c r="DT12">
+      <c r="DY12">
         <v>1</v>
       </c>
-      <c r="DU12">
+      <c r="DZ12">
         <v>72</v>
       </c>
-      <c r="DZ12">
+      <c r="EE12">
         <v>1</v>
       </c>
-      <c r="EA12">
+      <c r="EF12">
         <v>72</v>
       </c>
-      <c r="EB12" t="inlineStr">
+      <c r="EG12" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC12" t="inlineStr">
+      <c r="EH12" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG12" t="inlineStr">
+      <c r="EI12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL12" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH12">
+      <c r="EM12">
         <v>1</v>
       </c>
     </row>
@@ -4113,24 +4174,22 @@
         <v>49</v>
       </c>
       <c r="AT13">
+        <v>65</v>
+      </c>
+      <c r="AU13">
         <v>26.2</v>
       </c>
-      <c r="AU13">
+      <c r="AV13">
         <v>23.41</v>
       </c>
-      <c r="AV13">
+      <c r="AW13">
         <v>6.14</v>
       </c>
-      <c r="AW13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4138,134 +4197,142 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="BA13">
+      <c r="BB13">
+        <v>65</v>
+      </c>
+      <c r="BC13">
         <v>49</v>
       </c>
-      <c r="BB13">
+      <c r="BD13">
         <v>23.65</v>
       </c>
-      <c r="BC13">
+      <c r="BE13">
         <v>21.82</v>
       </c>
-      <c r="BD13">
+      <c r="BF13">
         <v>5.85</v>
       </c>
-      <c r="BE13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr">
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BY13">
+      <c r="CB13">
         <v>49</v>
       </c>
-      <c r="BZ13">
+      <c r="CC13">
         <v>65</v>
       </c>
-      <c r="CA13">
+      <c r="CD13">
         <v>12.91</v>
       </c>
-      <c r="CB13">
+      <c r="CE13">
         <v>9.880000000000001</v>
       </c>
-      <c r="CC13">
+      <c r="CF13">
         <v>4.15</v>
       </c>
-      <c r="CD13" t="inlineStr">
+      <c r="CG13" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX13">
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC13">
         <v>14</v>
       </c>
-      <c r="CY13">
+      <c r="DD13">
         <v>65</v>
       </c>
-      <c r="DB13">
+      <c r="DG13">
         <v>3</v>
       </c>
-      <c r="DC13">
+      <c r="DH13">
         <v>65</v>
       </c>
-      <c r="DF13">
+      <c r="DK13">
         <v>4</v>
       </c>
-      <c r="DG13">
+      <c r="DL13">
         <v>65</v>
       </c>
-      <c r="DH13">
+      <c r="DM13">
         <v>0</v>
       </c>
-      <c r="DI13">
+      <c r="DN13">
         <v>65</v>
       </c>
-      <c r="DP13">
+      <c r="DU13">
         <v>0</v>
       </c>
-      <c r="DQ13">
+      <c r="DV13">
         <v>65</v>
       </c>
-      <c r="DT13">
+      <c r="DY13">
         <v>3</v>
       </c>
-      <c r="DU13">
+      <c r="DZ13">
         <v>65</v>
       </c>
-      <c r="DZ13">
+      <c r="EE13">
         <v>2</v>
       </c>
-      <c r="EA13">
+      <c r="EF13">
         <v>65</v>
       </c>
-      <c r="EB13" t="inlineStr">
+      <c r="EG13" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC13" t="inlineStr">
+      <c r="EH13" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG13" t="inlineStr">
+      <c r="EI13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL13" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH13">
+      <c r="EM13">
         <v>1</v>
       </c>
     </row>
@@ -4459,24 +4526,22 @@
         <v>51</v>
       </c>
       <c r="AT14">
+        <v>68</v>
+      </c>
+      <c r="AU14">
         <v>27.26</v>
       </c>
-      <c r="AU14">
+      <c r="AV14">
         <v>22.22</v>
       </c>
-      <c r="AV14">
+      <c r="AW14">
         <v>6.5</v>
       </c>
-      <c r="AW14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4484,134 +4549,142 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="BA14">
+      <c r="BB14">
+        <v>68</v>
+      </c>
+      <c r="BC14">
         <v>51</v>
       </c>
-      <c r="BB14">
+      <c r="BD14">
         <v>24.59</v>
       </c>
-      <c r="BC14">
+      <c r="BE14">
         <v>22.53</v>
       </c>
-      <c r="BD14">
+      <c r="BF14">
         <v>5.41</v>
       </c>
-      <c r="BE14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BY14">
+      <c r="CB14">
         <v>51</v>
       </c>
-      <c r="BZ14">
+      <c r="CC14">
         <v>68</v>
       </c>
-      <c r="CA14">
+      <c r="CD14">
         <v>11.54</v>
       </c>
-      <c r="CB14">
+      <c r="CE14">
         <v>9.06</v>
       </c>
-      <c r="CC14">
+      <c r="CF14">
         <v>4.08</v>
       </c>
-      <c r="CD14" t="inlineStr">
+      <c r="CG14" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX14">
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC14">
         <v>23</v>
       </c>
-      <c r="CY14">
+      <c r="DD14">
         <v>68</v>
       </c>
-      <c r="DB14">
+      <c r="DG14">
         <v>2</v>
       </c>
-      <c r="DC14">
+      <c r="DH14">
         <v>68</v>
       </c>
-      <c r="DF14">
+      <c r="DK14">
         <v>5</v>
       </c>
-      <c r="DG14">
+      <c r="DL14">
         <v>68</v>
       </c>
-      <c r="DH14">
+      <c r="DM14">
         <v>2</v>
       </c>
-      <c r="DI14">
+      <c r="DN14">
         <v>68</v>
       </c>
-      <c r="DP14">
+      <c r="DU14">
         <v>8</v>
       </c>
-      <c r="DQ14">
+      <c r="DV14">
         <v>68</v>
       </c>
-      <c r="DT14">
+      <c r="DY14">
         <v>5</v>
       </c>
-      <c r="DU14">
+      <c r="DZ14">
         <v>68</v>
       </c>
-      <c r="DZ14">
+      <c r="EE14">
         <v>0</v>
       </c>
-      <c r="EA14">
+      <c r="EF14">
         <v>68</v>
       </c>
-      <c r="EB14" t="inlineStr">
+      <c r="EG14" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC14" t="inlineStr">
+      <c r="EH14" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG14" t="inlineStr">
+      <c r="EI14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL14" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH14">
+      <c r="EM14">
         <v>1</v>
       </c>
     </row>
@@ -4805,24 +4878,22 @@
         <v>56</v>
       </c>
       <c r="AT15">
+        <v>71</v>
+      </c>
+      <c r="AU15">
         <v>27.49</v>
       </c>
-      <c r="AU15">
+      <c r="AV15">
         <v>19.52</v>
       </c>
-      <c r="AV15">
+      <c r="AW15">
         <v>5.11</v>
       </c>
-      <c r="AW15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4830,134 +4901,142 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="BA15">
+      <c r="BB15">
+        <v>71</v>
+      </c>
+      <c r="BC15">
         <v>56</v>
       </c>
-      <c r="BB15">
+      <c r="BD15">
         <v>23.65</v>
       </c>
-      <c r="BC15">
+      <c r="BE15">
         <v>21.45</v>
       </c>
-      <c r="BD15">
+      <c r="BF15">
         <v>5.13</v>
       </c>
-      <c r="BE15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BY15">
+      <c r="CB15">
         <v>56</v>
       </c>
-      <c r="BZ15">
+      <c r="CC15">
         <v>71</v>
       </c>
-      <c r="CA15">
+      <c r="CD15">
         <v>12.58</v>
       </c>
-      <c r="CB15">
+      <c r="CE15">
         <v>8.5</v>
       </c>
-      <c r="CC15">
+      <c r="CF15">
         <v>4.09</v>
       </c>
-      <c r="CD15" t="inlineStr">
+      <c r="CG15" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX15">
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC15">
         <v>36</v>
       </c>
-      <c r="CY15">
+      <c r="DD15">
         <v>71</v>
       </c>
-      <c r="DB15">
+      <c r="DG15">
         <v>5</v>
       </c>
-      <c r="DC15">
+      <c r="DH15">
         <v>71</v>
       </c>
-      <c r="DF15">
+      <c r="DK15">
         <v>6</v>
       </c>
-      <c r="DG15">
+      <c r="DL15">
         <v>71</v>
       </c>
-      <c r="DH15">
+      <c r="DM15">
         <v>6</v>
       </c>
-      <c r="DI15">
+      <c r="DN15">
         <v>71</v>
       </c>
-      <c r="DP15">
+      <c r="DU15">
         <v>0</v>
       </c>
-      <c r="DQ15">
+      <c r="DV15">
         <v>71</v>
       </c>
-      <c r="DT15">
+      <c r="DY15">
         <v>5</v>
       </c>
-      <c r="DU15">
+      <c r="DZ15">
         <v>71</v>
       </c>
-      <c r="DZ15">
+      <c r="EE15">
         <v>8</v>
       </c>
-      <c r="EA15">
+      <c r="EF15">
         <v>71</v>
       </c>
-      <c r="EB15" t="inlineStr">
+      <c r="EG15" t="inlineStr">
         <is>
           <t>D2 antipsychotic</t>
         </is>
       </c>
-      <c r="EC15" t="inlineStr">
+      <c r="EH15" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG15" t="inlineStr">
+      <c r="EI15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL15" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH15">
+      <c r="EM15">
         <v>1</v>
       </c>
     </row>
@@ -5067,69 +5146,69 @@
           <t>34</t>
         </is>
       </c>
-      <c r="CX16">
+      <c r="DC16">
         <v>16</v>
       </c>
-      <c r="CY16">
+      <c r="DD16">
         <v>34</v>
       </c>
-      <c r="CZ16">
+      <c r="DE16">
         <v>0</v>
       </c>
-      <c r="DA16">
+      <c r="DF16">
         <v>34</v>
       </c>
-      <c r="DB16">
+      <c r="DG16">
         <v>0</v>
       </c>
-      <c r="DC16">
+      <c r="DH16">
         <v>34</v>
       </c>
-      <c r="DD16">
+      <c r="DI16">
         <v>2</v>
       </c>
-      <c r="DE16">
+      <c r="DJ16">
         <v>34</v>
       </c>
-      <c r="DF16">
+      <c r="DK16">
         <v>7</v>
       </c>
-      <c r="DG16">
+      <c r="DL16">
         <v>34</v>
       </c>
-      <c r="DH16">
+      <c r="DM16">
         <v>0</v>
       </c>
-      <c r="DI16">
+      <c r="DN16">
         <v>34</v>
       </c>
-      <c r="DJ16">
+      <c r="DO16">
         <v>5</v>
       </c>
-      <c r="DK16">
+      <c r="DP16">
         <v>34</v>
       </c>
-      <c r="EB16" t="inlineStr">
+      <c r="EG16" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC16" t="inlineStr">
+      <c r="EH16" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr">
+      <c r="EI16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL16" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH16">
+      <c r="EM16">
         <v>1</v>
       </c>
     </row>
@@ -5239,69 +5318,69 @@
           <t>35</t>
         </is>
       </c>
-      <c r="CX17">
+      <c r="DC17">
         <v>34</v>
       </c>
-      <c r="CY17">
+      <c r="DD17">
         <v>35</v>
       </c>
-      <c r="CZ17">
+      <c r="DE17">
         <v>5</v>
       </c>
-      <c r="DA17">
+      <c r="DF17">
         <v>35</v>
       </c>
-      <c r="DB17">
+      <c r="DG17">
         <v>0</v>
       </c>
-      <c r="DC17">
+      <c r="DH17">
         <v>35</v>
       </c>
-      <c r="DD17">
+      <c r="DI17">
         <v>10</v>
       </c>
-      <c r="DE17">
+      <c r="DJ17">
         <v>35</v>
       </c>
-      <c r="DF17">
+      <c r="DK17">
         <v>4</v>
       </c>
-      <c r="DG17">
+      <c r="DL17">
         <v>35</v>
       </c>
-      <c r="DH17">
+      <c r="DM17">
         <v>12</v>
       </c>
-      <c r="DI17">
+      <c r="DN17">
         <v>35</v>
       </c>
-      <c r="DJ17">
+      <c r="DO17">
         <v>21</v>
       </c>
-      <c r="DK17">
+      <c r="DP17">
         <v>35</v>
       </c>
-      <c r="EB17" t="inlineStr">
+      <c r="EG17" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC17" t="inlineStr">
+      <c r="EH17" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG17" t="inlineStr">
+      <c r="EI17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL17" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH17">
+      <c r="EM17">
         <v>1</v>
       </c>
     </row>
@@ -5411,69 +5490,69 @@
           <t>36</t>
         </is>
       </c>
-      <c r="CX18">
+      <c r="DC18">
         <v>15</v>
       </c>
-      <c r="CY18">
+      <c r="DD18">
         <v>36</v>
       </c>
-      <c r="CZ18">
+      <c r="DE18">
         <v>0</v>
       </c>
-      <c r="DA18">
+      <c r="DF18">
         <v>36</v>
       </c>
-      <c r="DB18">
+      <c r="DG18">
         <v>3</v>
       </c>
-      <c r="DC18">
+      <c r="DH18">
         <v>36</v>
       </c>
-      <c r="DD18">
+      <c r="DI18">
         <v>1</v>
       </c>
-      <c r="DE18">
+      <c r="DJ18">
         <v>36</v>
       </c>
-      <c r="DF18">
+      <c r="DK18">
         <v>1</v>
       </c>
-      <c r="DG18">
+      <c r="DL18">
         <v>36</v>
       </c>
-      <c r="DH18">
+      <c r="DM18">
         <v>0</v>
       </c>
-      <c r="DI18">
+      <c r="DN18">
         <v>36</v>
       </c>
-      <c r="DJ18">
+      <c r="DO18">
         <v>5</v>
       </c>
-      <c r="DK18">
+      <c r="DP18">
         <v>36</v>
       </c>
-      <c r="EB18" t="inlineStr">
+      <c r="EG18" t="inlineStr">
         <is>
           <t>D2 antipsychotic</t>
         </is>
       </c>
-      <c r="EC18" t="inlineStr">
+      <c r="EH18" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG18" t="inlineStr">
+      <c r="EI18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL18" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH18">
+      <c r="EM18">
         <v>1</v>
       </c>
     </row>
@@ -5578,63 +5657,63 @@
           <t>63</t>
         </is>
       </c>
-      <c r="CX19">
+      <c r="DC19">
         <v>2</v>
       </c>
-      <c r="CY19">
+      <c r="DD19">
         <v>63</v>
       </c>
-      <c r="DD19">
+      <c r="DI19">
         <v>1</v>
       </c>
-      <c r="DE19">
+      <c r="DJ19">
         <v>63</v>
       </c>
-      <c r="DH19">
+      <c r="DM19">
         <v>1</v>
       </c>
-      <c r="DI19">
+      <c r="DN19">
         <v>63</v>
       </c>
-      <c r="DJ19">
+      <c r="DO19">
         <v>0</v>
       </c>
-      <c r="DK19">
+      <c r="DP19">
         <v>63</v>
       </c>
-      <c r="DN19">
+      <c r="DS19">
         <v>1</v>
       </c>
-      <c r="DO19">
+      <c r="DT19">
         <v>59</v>
       </c>
-      <c r="EB19" t="inlineStr">
+      <c r="EG19" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC19" t="inlineStr">
+      <c r="EH19" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EE19">
+      <c r="EI19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EJ19">
         <v>1.248958333333333</v>
       </c>
-      <c r="EF19">
+      <c r="EK19">
         <v>2.100625000000001</v>
       </c>
-      <c r="EG19" t="inlineStr">
+      <c r="EL19" t="inlineStr">
         <is>
           <t>Tsukada (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH19">
+      <c r="EM19">
         <v>2</v>
       </c>
     </row>
@@ -5749,63 +5828,63 @@
           <t>63</t>
         </is>
       </c>
-      <c r="CX20">
+      <c r="DC20">
         <v>32</v>
       </c>
-      <c r="CY20">
+      <c r="DD20">
         <v>63</v>
       </c>
-      <c r="DD20">
+      <c r="DI20">
         <v>7</v>
       </c>
-      <c r="DE20">
+      <c r="DJ20">
         <v>63</v>
       </c>
-      <c r="DH20">
+      <c r="DM20">
         <v>16</v>
       </c>
-      <c r="DI20">
+      <c r="DN20">
         <v>63</v>
       </c>
-      <c r="DJ20">
+      <c r="DO20">
         <v>16</v>
       </c>
-      <c r="DK20">
+      <c r="DP20">
         <v>63</v>
       </c>
-      <c r="DN20">
+      <c r="DS20">
         <v>5</v>
       </c>
-      <c r="DO20">
+      <c r="DT20">
         <v>62</v>
       </c>
-      <c r="EB20" t="inlineStr">
+      <c r="EG20" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC20" t="inlineStr">
+      <c r="EH20" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EE20">
+      <c r="EI20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EJ20">
         <v>1.248958333333333</v>
       </c>
-      <c r="EF20">
+      <c r="EK20">
         <v>2.100625000000001</v>
       </c>
-      <c r="EG20" t="inlineStr">
+      <c r="EL20" t="inlineStr">
         <is>
           <t>Tsukada (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH20">
+      <c r="EM20">
         <v>2</v>
       </c>
     </row>
@@ -5915,57 +5994,57 @@
           <t>12</t>
         </is>
       </c>
-      <c r="CX21">
+      <c r="DC21">
         <v>1</v>
       </c>
-      <c r="CY21">
+      <c r="DD21">
         <v>12</v>
       </c>
-      <c r="DH21">
+      <c r="DM21">
         <v>1</v>
       </c>
-      <c r="DI21">
+      <c r="DN21">
         <v>12</v>
       </c>
-      <c r="DJ21">
+      <c r="DO21">
         <v>0</v>
       </c>
-      <c r="DK21">
+      <c r="DP21">
         <v>12</v>
       </c>
-      <c r="DL21">
+      <c r="DQ21">
         <v>0</v>
       </c>
-      <c r="DM21">
+      <c r="DR21">
         <v>12</v>
       </c>
-      <c r="DN21">
+      <c r="DS21">
         <v>0</v>
       </c>
-      <c r="DO21">
+      <c r="DT21">
         <v>12</v>
       </c>
-      <c r="EB21" t="inlineStr">
+      <c r="EG21" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC21" t="inlineStr">
+      <c r="EH21" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG21" t="inlineStr">
+      <c r="EI21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL21" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EH21">
+      <c r="EM21">
         <v>2</v>
       </c>
     </row>
@@ -6075,57 +6154,57 @@
           <t>12</t>
         </is>
       </c>
-      <c r="CX22">
+      <c r="DC22">
         <v>1</v>
       </c>
-      <c r="CY22">
+      <c r="DD22">
         <v>12</v>
       </c>
-      <c r="DH22">
+      <c r="DM22">
         <v>0</v>
       </c>
-      <c r="DI22">
+      <c r="DN22">
         <v>12</v>
       </c>
-      <c r="DJ22">
+      <c r="DO22">
         <v>1</v>
       </c>
-      <c r="DK22">
+      <c r="DP22">
         <v>12</v>
       </c>
-      <c r="DL22">
+      <c r="DQ22">
         <v>0</v>
       </c>
-      <c r="DM22">
+      <c r="DR22">
         <v>12</v>
       </c>
-      <c r="DN22">
+      <c r="DS22">
         <v>0</v>
       </c>
-      <c r="DO22">
+      <c r="DT22">
         <v>12</v>
       </c>
-      <c r="EB22" t="inlineStr">
+      <c r="EG22" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC22" t="inlineStr">
+      <c r="EH22" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG22" t="inlineStr">
+      <c r="EI22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL22" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EH22">
+      <c r="EM22">
         <v>2</v>
       </c>
     </row>
@@ -6235,57 +6314,57 @@
           <t>24</t>
         </is>
       </c>
-      <c r="CX23">
+      <c r="DC23">
         <v>1</v>
       </c>
-      <c r="CY23">
+      <c r="DD23">
         <v>24</v>
       </c>
-      <c r="DH23">
+      <c r="DM23">
         <v>0</v>
       </c>
-      <c r="DI23">
+      <c r="DN23">
         <v>24</v>
       </c>
-      <c r="DJ23">
+      <c r="DO23">
         <v>0</v>
       </c>
-      <c r="DK23">
+      <c r="DP23">
         <v>24</v>
       </c>
-      <c r="DL23">
+      <c r="DQ23">
         <v>0</v>
       </c>
-      <c r="DM23">
+      <c r="DR23">
         <v>24</v>
       </c>
-      <c r="DN23">
+      <c r="DS23">
         <v>0</v>
       </c>
-      <c r="DO23">
+      <c r="DT23">
         <v>24</v>
       </c>
-      <c r="EB23" t="inlineStr">
+      <c r="EG23" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC23" t="inlineStr">
+      <c r="EH23" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG23" t="inlineStr">
+      <c r="EI23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL23" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EH23">
+      <c r="EM23">
         <v>2</v>
       </c>
     </row>
@@ -6375,33 +6454,33 @@
           <t>16</t>
         </is>
       </c>
-      <c r="CX24">
+      <c r="DC24">
         <v>6</v>
       </c>
-      <c r="CY24">
+      <c r="DD24">
         <v>15</v>
       </c>
-      <c r="EB24" t="inlineStr">
+      <c r="EG24" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC24" t="inlineStr">
+      <c r="EH24" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG24" t="inlineStr">
+      <c r="EI24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL24" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH24">
+      <c r="EM24">
         <v>3</v>
       </c>
     </row>
@@ -6491,33 +6570,33 @@
           <t>16</t>
         </is>
       </c>
-      <c r="CX25">
+      <c r="DC25">
         <v>1</v>
       </c>
-      <c r="CY25">
+      <c r="DD25">
         <v>13</v>
       </c>
-      <c r="EB25" t="inlineStr">
+      <c r="EG25" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC25" t="inlineStr">
+      <c r="EH25" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG25" t="inlineStr">
+      <c r="EI25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL25" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH25">
+      <c r="EM25">
         <v>3</v>
       </c>
     </row>
@@ -6607,33 +6686,33 @@
           <t>16</t>
         </is>
       </c>
-      <c r="CX26">
+      <c r="DC26">
         <v>2</v>
       </c>
-      <c r="CY26">
+      <c r="DD26">
         <v>14</v>
       </c>
-      <c r="EB26" t="inlineStr">
+      <c r="EG26" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC26" t="inlineStr">
+      <c r="EH26" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG26" t="inlineStr">
+      <c r="EI26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL26" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH26">
+      <c r="EM26">
         <v>3</v>
       </c>
     </row>
